--- a/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>AMPS</t>
   </si>
@@ -656,249 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E8" s="3">
         <v>45100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>44000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20900</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E9" s="3">
         <v>7800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4600</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E10" s="3">
         <v>37300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>38900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,28 +1040,31 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>300</v>
       </c>
       <c r="J14" s="3">
         <v>300</v>
@@ -1054,84 +1073,90 @@
         <v>300</v>
       </c>
       <c r="L14" s="3">
+        <v>300</v>
+      </c>
+      <c r="M14" s="3">
         <v>4200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6800</v>
       </c>
       <c r="K15" s="3">
         <v>6800</v>
       </c>
       <c r="L15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M15" s="3">
         <v>5300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5400</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1173,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E17" s="3">
         <v>34200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>10900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,125 +1307,132 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6000</v>
+        <v>-34900</v>
       </c>
       <c r="E20" s="3">
-        <v>-7500</v>
+        <v>-5600</v>
       </c>
       <c r="F20" s="3">
-        <v>4500</v>
+        <v>-7100</v>
       </c>
       <c r="G20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H20" s="3">
         <v>66500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-104900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>77300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>60200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18600</v>
+        <v>-24800</v>
       </c>
       <c r="E21" s="3">
-        <v>17500</v>
+        <v>19000</v>
       </c>
       <c r="F21" s="3">
-        <v>16100</v>
+        <v>17900</v>
       </c>
       <c r="G21" s="3">
+        <v>16500</v>
+      </c>
+      <c r="H21" s="3">
         <v>74800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-87100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>96700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>67100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>400</v>
@@ -1402,17 +1441,17 @@
         <v>400</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1428,120 +1467,129 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E23" s="3">
         <v>4800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>65600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-94700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>82300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1641,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-96600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>81700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>60100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>67500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-97000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>84300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>59900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +1977,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6000</v>
+        <v>34900</v>
       </c>
       <c r="E32" s="3">
-        <v>7500</v>
+        <v>5600</v>
       </c>
       <c r="F32" s="3">
-        <v>-4500</v>
+        <v>7100</v>
       </c>
       <c r="G32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="H32" s="3">
         <v>-66500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>104900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-77300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-60200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6700</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>67500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-97000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>84300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>59900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2145,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>67500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-97000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>84300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>59900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,44 +2308,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160800</v>
+      </c>
+      <c r="E41" s="3">
         <v>68200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>193000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>290900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>295100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>318200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>326000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2362,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,44 +2418,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E43" s="3">
         <v>23400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,8 +2474,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,44 +2530,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E45" s="3">
         <v>6500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>9200</v>
       </c>
       <c r="K45" s="3">
         <v>9200</v>
       </c>
       <c r="L45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M45" s="3">
         <v>12400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,44 +2586,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>228800</v>
+      </c>
+      <c r="E46" s="3">
         <v>98100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>106300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>93400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>215100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>315500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>316400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>335800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>344400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,44 +2698,47 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1792900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1557200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1494400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1099600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>788100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>764900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>746000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>745700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>727700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>522200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2641,50 +2748,53 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E49" s="3">
         <v>47100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>47400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11400</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,14 +2804,17 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,44 +2922,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E52" s="3">
         <v>38700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,44 +3034,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2090300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1784400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1735400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1657400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1376900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1130300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1106100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1104300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1113200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>809900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>586100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,44 +3136,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,50 +3184,53 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E58" s="3">
         <v>34100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>32500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>30000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3107,50 +3240,53 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E59" s="3">
         <v>57500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>58200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,44 +3302,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E60" s="3">
         <v>96600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>68200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,44 +3358,47 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1163300</v>
+      </c>
+      <c r="E61" s="3">
         <v>908000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>878500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>835700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>634600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>527700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>522600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>521900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>524800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>503600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>364800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3272,44 +3414,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E62" s="3">
         <v>253100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>256400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>235200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>211000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>190300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>149300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>214000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,44 +3638,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1643300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1318500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1287400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1224200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>952800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>788200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>706000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>738400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>808300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>620800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>469600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3694,14 +3861,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>283200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>204900</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,44 +3940,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-28100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-33500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-40300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-113800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-16800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-40900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-101400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-90600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,44 +4164,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>447100</v>
+      </c>
+      <c r="E76" s="3">
         <v>465900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>448000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>433200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>424100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>342100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>400000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>365900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>304900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-94100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-88500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4276,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>67500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-97000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>84300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>59900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,61 +4417,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E83" s="3">
         <v>13700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6800</v>
       </c>
       <c r="K83" s="3">
         <v>6800</v>
       </c>
       <c r="L83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5400</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4751,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E89" s="3">
         <v>23600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,61 +4831,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +4997,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-158300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-319400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-118300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-124400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4887,19 +5120,22 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,52 +5299,55 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E100" s="3">
         <v>31500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>42600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>190000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>295400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>198400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>125700</v>
-      </c>
-      <c r="O100" s="3">
-        <v>19700</v>
       </c>
       <c r="P100" s="3">
         <v>19700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>19700</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5355,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,57 +5411,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-115200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-98000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>291100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>AMPS</t>
   </si>
@@ -656,261 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E8" s="3">
         <v>34200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>44000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20900</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4600</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E10" s="3">
         <v>25900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>16300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +944,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,31 +1060,34 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
-      </c>
-      <c r="J14" s="3">
-        <v>300</v>
       </c>
       <c r="K14" s="3">
         <v>300</v>
@@ -1076,87 +1096,93 @@
         <v>300</v>
       </c>
       <c r="M14" s="3">
+        <v>300</v>
+      </c>
+      <c r="N14" s="3">
         <v>4200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E15" s="3">
         <v>15600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>6800</v>
       </c>
       <c r="L15" s="3">
         <v>6800</v>
       </c>
       <c r="M15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N15" s="3">
         <v>5300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,120 +1200,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E17" s="3">
         <v>39700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14400</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,120 +1341,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-34900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>66500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-104900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>77300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>60200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6700</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>74800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-87100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>96700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>67100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1444,17 +1484,17 @@
         <v>400</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1470,126 +1510,135 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>65600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-94700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>82300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-96600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>60100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-97000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>84300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>59900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,120 +2047,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E32" s="3">
         <v>34900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-66500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>104900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-77300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-60200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6700</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-97000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>84300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>59900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-97000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>84300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>59900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,47 +2395,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>173300</v>
+      </c>
+      <c r="E41" s="3">
         <v>160800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>290900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>295100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>318200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>326000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2452,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,47 +2511,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E43" s="3">
         <v>17100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,47 +2629,50 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E45" s="3">
         <v>50900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>9200</v>
       </c>
       <c r="L45" s="3">
         <v>9200</v>
       </c>
       <c r="M45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="N45" s="3">
         <v>12400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,47 +2688,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E46" s="3">
         <v>228800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>98100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>106300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>93400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>215100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>315500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>316400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>335800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>344400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>58200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2701,47 +2806,50 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1929100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1792900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1600600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1557200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1494400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1099600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>788100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>764900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>746000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>745700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>727700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>522200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,53 +2859,56 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E49" s="3">
         <v>47600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>47100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>47600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2807,14 +2918,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,47 +3042,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E52" s="3">
         <v>21100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,47 +3160,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2218500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2090300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1784400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1735400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1657400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1376900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1130300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1106100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1104300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1113200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>809900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>586100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,47 +3267,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3187,53 +3318,56 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E58" s="3">
         <v>39600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>32100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>30000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>33900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,53 +3377,56 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E59" s="3">
         <v>59600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,47 +3442,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E60" s="3">
         <v>106500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>97400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>68200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,47 +3501,50 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1253800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1163300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>908000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>878500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>835700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>634600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>527700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>522600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>521900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>524800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>503600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>364800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3417,47 +3560,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E62" s="3">
         <v>295500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>253100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>256400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>235200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>211000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>190300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>121100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>149300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>214000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,47 +3796,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1760900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1643300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1318500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1287400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1224200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>952800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>788200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>706000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>738400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>808300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>620800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>469600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3864,14 +4032,14 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>283200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>204900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,47 +4114,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-55300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-40300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-113800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-16800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-40900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-101400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-97300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,47 +4350,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>457500</v>
+      </c>
+      <c r="E76" s="3">
         <v>447100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>465900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>448000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>433200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>424100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>342100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>400000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>365900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>304900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-94100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-88500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-97000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>84300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>59900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,64 +4616,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E83" s="3">
         <v>15600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6800</v>
       </c>
       <c r="L83" s="3">
         <v>6800</v>
       </c>
       <c r="M83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,64 +4968,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>30300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,64 +5052,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,64 +5227,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-141900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-158300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-55200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-53900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-319400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-118300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-124400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26600</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5123,19 +5357,22 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-22500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,55 +5545,58 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E100" s="3">
         <v>262900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>31500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>190000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>295400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>198400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>125700</v>
-      </c>
-      <c r="P100" s="3">
-        <v>19700</v>
       </c>
       <c r="Q100" s="3">
         <v>19700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>19700</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5414,60 +5663,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E102" s="3">
         <v>134900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-115200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-98000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>291100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>AMPS</t>
   </si>
@@ -656,274 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E8" s="3">
         <v>40700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>44000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20900</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E9" s="3">
         <v>10900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4600</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E10" s="3">
         <v>29800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,34 +1080,37 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>300</v>
       </c>
       <c r="L14" s="3">
         <v>300</v>
@@ -1099,90 +1119,96 @@
         <v>300</v>
       </c>
       <c r="N14" s="3">
+        <v>300</v>
+      </c>
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E15" s="3">
         <v>16100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13700</v>
-      </c>
-      <c r="L15" s="3">
-        <v>6800</v>
       </c>
       <c r="M15" s="3">
         <v>6800</v>
       </c>
       <c r="N15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O15" s="3">
         <v>5300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5400</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E17" s="3">
         <v>42300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14400</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,126 +1375,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-34900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>66500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-104900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>77300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>60200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E21" s="3">
         <v>25500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>74800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-87100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>96700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>67100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>23300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1487,17 +1527,17 @@
         <v>400</v>
       </c>
       <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,132 +1553,141 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>65600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-94700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>82300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>60000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E26" s="3">
         <v>4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-40000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>67100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-96600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>60100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E27" s="3">
         <v>7500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>67500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-97000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>84300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>59900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,126 +2117,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>34900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-66500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>104900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-77300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-60200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E33" s="3">
         <v>7500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>67500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-97000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>84300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>59900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E35" s="3">
         <v>7500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>67500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-97000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>84300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>59900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,50 +2482,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E41" s="3">
         <v>173300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>160800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>290900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>295100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>318200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>326000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2542,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,50 +2604,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E43" s="3">
         <v>20100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,50 +2728,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E45" s="3">
         <v>23400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>9200</v>
       </c>
       <c r="M45" s="3">
         <v>9200</v>
       </c>
       <c r="N45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,50 +2790,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E46" s="3">
         <v>216700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>228800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>98100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>93400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>215100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>315500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>316400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>335800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>344400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2809,50 +2914,53 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1933200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1929100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1792900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1557200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1494400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1099600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>788100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>764900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>746000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>745700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>727700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>522200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,56 +2970,59 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E49" s="3">
         <v>47300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>47600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>47800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>47600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11400</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2921,14 +3032,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,50 +3162,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E52" s="3">
         <v>25400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,50 +3286,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2131900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2218500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2090300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1784400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1735400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1657400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1376900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1130300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1106100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1104300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1113200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>809900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>586100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,50 +3398,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3321,56 +3452,59 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E58" s="3">
         <v>73400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>39600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>32500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>33900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,56 +3514,59 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E59" s="3">
         <v>65200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,50 +3582,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E60" s="3">
         <v>146100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>106500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,50 +3644,53 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1180200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1253800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1163300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>908000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>878500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>835700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>634600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>527700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>522600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>521900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>524800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>503600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>364800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3563,50 +3706,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>256600</v>
+      </c>
+      <c r="E62" s="3">
         <v>286100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>295500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>253100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>256400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>235200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>211000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>190300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>149300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>214000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,50 +3954,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1641400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1760900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1643300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1318500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1287400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1224200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>952800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>788200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>706000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>738400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>808300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>620800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>469600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4035,14 +4203,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>283200</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>204900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,50 +4288,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-47800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-40300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-113800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-16800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-40900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-101400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-97300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-90600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,50 +4536,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>490500</v>
+      </c>
+      <c r="E76" s="3">
         <v>457500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>447100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>465900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>448000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>433200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>424100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>342100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>400000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>365900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>304900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-94100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-88500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E81" s="3">
         <v>7500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>67500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-97000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>84300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>59900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,67 +4815,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E83" s="3">
         <v>16100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6800</v>
       </c>
       <c r="M83" s="3">
         <v>6800</v>
       </c>
       <c r="N83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5400</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-37100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-24800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-141900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-158300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-53900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-319400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-124400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-26600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5360,19 +5594,22 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-22500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,58 +5791,61 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E100" s="3">
         <v>122000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>262900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>42600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>190000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>295400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>198400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>125700</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>19700</v>
       </c>
       <c r="R100" s="3">
         <v>19700</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>19700</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5666,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-111200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>134900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-115200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-98000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>291100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>AMPS</t>
   </si>
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E8" s="3">
         <v>52500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>44000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20900</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E9" s="3">
         <v>11300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E10" s="3">
         <v>41200</v>
       </c>
-      <c r="E10" s="3">
-        <v>29800</v>
-      </c>
       <c r="F10" s="3">
+        <v>29700</v>
+      </c>
+      <c r="G10" s="3">
         <v>25900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,37 +1100,40 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500</v>
+        <v>-8100</v>
       </c>
       <c r="E14" s="3">
-        <v>1100</v>
+        <v>-10600</v>
       </c>
       <c r="F14" s="3">
-        <v>1500</v>
+        <v>-25200</v>
       </c>
       <c r="G14" s="3">
-        <v>300</v>
+        <v>4700</v>
       </c>
       <c r="H14" s="3">
-        <v>1400</v>
+        <v>-3200</v>
       </c>
       <c r="I14" s="3">
-        <v>1500</v>
+        <v>-1400</v>
       </c>
       <c r="J14" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K14" s="3">
         <v>5300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
-      </c>
-      <c r="L14" s="3">
-        <v>300</v>
       </c>
       <c r="M14" s="3">
         <v>300</v>
@@ -1122,31 +1142,34 @@
         <v>300</v>
       </c>
       <c r="O14" s="3">
+        <v>300</v>
+      </c>
+      <c r="P14" s="3">
         <v>4200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,61 +1177,64 @@
         <v>17200</v>
       </c>
       <c r="E15" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F15" s="3">
         <v>16100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>6800</v>
       </c>
       <c r="N15" s="3">
         <v>6800</v>
       </c>
       <c r="O15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P15" s="3">
         <v>5300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5400</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>35500</v>
+        <v>41300</v>
       </c>
       <c r="E17" s="3">
-        <v>42300</v>
+        <v>34300</v>
       </c>
       <c r="F17" s="3">
-        <v>39700</v>
+        <v>41400</v>
       </c>
       <c r="G17" s="3">
-        <v>34200</v>
+        <v>36100</v>
       </c>
       <c r="H17" s="3">
-        <v>34500</v>
+        <v>33900</v>
       </c>
       <c r="I17" s="3">
-        <v>29100</v>
+        <v>33100</v>
       </c>
       <c r="J17" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K17" s="3">
         <v>27300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14400</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>17000</v>
+        <v>17400</v>
       </c>
       <c r="E18" s="3">
-        <v>-1600</v>
+        <v>18200</v>
       </c>
       <c r="F18" s="3">
-        <v>-5500</v>
+        <v>-700</v>
       </c>
       <c r="G18" s="3">
-        <v>10900</v>
+        <v>-1900</v>
       </c>
       <c r="H18" s="3">
-        <v>12000</v>
+        <v>11200</v>
       </c>
       <c r="I18" s="3">
-        <v>300</v>
+        <v>13400</v>
       </c>
       <c r="J18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,171 +1409,178 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4500</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>10900</v>
+        <v>-1100</v>
       </c>
       <c r="F20" s="3">
-        <v>-34900</v>
+        <v>-700</v>
       </c>
       <c r="G20" s="3">
-        <v>-5600</v>
+        <v>18000</v>
       </c>
       <c r="H20" s="3">
-        <v>-7100</v>
+        <v>300</v>
       </c>
       <c r="I20" s="3">
-        <v>4900</v>
+        <v>1800</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>66500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-104900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>77300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>60200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6700</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>29700</v>
+        <v>34300</v>
       </c>
       <c r="E21" s="3">
-        <v>25500</v>
+        <v>36500</v>
       </c>
       <c r="F21" s="3">
-        <v>-24800</v>
+        <v>16100</v>
       </c>
       <c r="G21" s="3">
-        <v>19000</v>
+        <v>-4400</v>
       </c>
       <c r="H21" s="3">
-        <v>17900</v>
+        <v>24500</v>
       </c>
       <c r="I21" s="3">
-        <v>16500</v>
+        <v>24600</v>
       </c>
       <c r="J21" s="3">
+        <v>13100</v>
+      </c>
+      <c r="K21" s="3">
         <v>74800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-87100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>96700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>67100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>23300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>21800</v>
       </c>
       <c r="E22" s="3">
-        <v>400</v>
+        <v>17900</v>
       </c>
       <c r="F22" s="3">
-        <v>400</v>
+        <v>16200</v>
       </c>
       <c r="G22" s="3">
-        <v>400</v>
+        <v>17300</v>
       </c>
       <c r="H22" s="3">
-        <v>400</v>
+        <v>9200</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>8500</v>
       </c>
       <c r="J22" s="3">
-        <v>400</v>
+        <v>12400</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
       </c>
       <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1556,138 +1596,147 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>12100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>65600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>82300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>60000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E26" s="3">
         <v>33100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>67100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-96600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>60100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>37500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>67500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-97000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>84300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>59900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4500</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-10900</v>
+        <v>1100</v>
       </c>
       <c r="F32" s="3">
-        <v>34900</v>
+        <v>700</v>
       </c>
       <c r="G32" s="3">
-        <v>5600</v>
+        <v>-18000</v>
       </c>
       <c r="H32" s="3">
-        <v>7100</v>
+        <v>-300</v>
       </c>
       <c r="I32" s="3">
-        <v>-4900</v>
+        <v>-1800</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-66500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>104900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-77300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-60200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6700</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>37500</v>
+        <v>17600</v>
       </c>
       <c r="E33" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F33" s="3">
         <v>7500</v>
       </c>
-      <c r="F33" s="3">
-        <v>-27000</v>
-      </c>
       <c r="G33" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="H33" s="3">
         <v>5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>67500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-97000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>84300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>59900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>37500</v>
+        <v>17600</v>
       </c>
       <c r="E35" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F35" s="3">
         <v>7500</v>
       </c>
-      <c r="F35" s="3">
-        <v>-27000</v>
-      </c>
       <c r="G35" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="H35" s="3">
         <v>5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>67500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-97000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>84300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>59900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E41" s="3">
         <v>78400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>173300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>160800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>290900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>295100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>318200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>326000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,53 +2697,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E43" s="3">
         <v>31800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,31 +2762,34 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2731,53 +2827,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9700</v>
+        <v>6200</v>
       </c>
       <c r="E45" s="3">
-        <v>23400</v>
+        <v>8600</v>
       </c>
       <c r="F45" s="3">
-        <v>50900</v>
+        <v>5800</v>
       </c>
       <c r="G45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I45" s="3">
         <v>6500</v>
       </c>
-      <c r="H45" s="3">
-        <v>10200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7800</v>
-      </c>
       <c r="J45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K45" s="3">
         <v>8600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>9200</v>
       </c>
       <c r="N45" s="3">
         <v>9200</v>
       </c>
       <c r="O45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E46" s="3">
         <v>119900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>216700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>228800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>93400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>215100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>315500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>316400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>335800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>344400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>58200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,31 +2957,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2917,53 +3022,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2019100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1933200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1929100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1792900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1557200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1494400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1099600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>788100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>764900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>746000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>745700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>727700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>522200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2973,59 +3081,62 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E49" s="3">
         <v>48500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>47300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>47400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>47800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>47600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3035,14 +3146,17 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,53 +3282,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>30300</v>
+        <v>20800</v>
       </c>
       <c r="E52" s="3">
-        <v>25400</v>
+        <v>21000</v>
       </c>
       <c r="F52" s="3">
-        <v>21100</v>
+        <v>22800</v>
       </c>
       <c r="G52" s="3">
-        <v>38700</v>
+        <v>20600</v>
       </c>
       <c r="H52" s="3">
-        <v>24500</v>
+        <v>19600</v>
       </c>
       <c r="I52" s="3">
-        <v>21800</v>
+        <v>19400</v>
       </c>
       <c r="J52" s="3">
+        <v>19600</v>
+      </c>
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2240100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2131900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2218500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2090300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1784400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1735400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1657400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1376900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1130300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1106100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1104300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1113200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>809900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>586100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,53 +3529,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E57" s="3">
         <v>7500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,59 +3586,62 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>73600</v>
+        <v>148900</v>
       </c>
       <c r="E58" s="3">
-        <v>73400</v>
+        <v>78100</v>
       </c>
       <c r="F58" s="3">
-        <v>39600</v>
+        <v>79700</v>
       </c>
       <c r="G58" s="3">
-        <v>34100</v>
+        <v>46500</v>
       </c>
       <c r="H58" s="3">
-        <v>32100</v>
+        <v>37800</v>
       </c>
       <c r="I58" s="3">
-        <v>32500</v>
+        <v>35600</v>
       </c>
       <c r="J58" s="3">
+        <v>36300</v>
+      </c>
+      <c r="K58" s="3">
         <v>30000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>21100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>33900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3517,59 +3651,62 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>50800</v>
+        <v>59000</v>
       </c>
       <c r="E59" s="3">
-        <v>65200</v>
+        <v>31100</v>
       </c>
       <c r="F59" s="3">
-        <v>59600</v>
+        <v>44900</v>
       </c>
       <c r="G59" s="3">
-        <v>57500</v>
+        <v>44000</v>
       </c>
       <c r="H59" s="3">
-        <v>59700</v>
+        <v>45300</v>
       </c>
       <c r="I59" s="3">
-        <v>58200</v>
+        <v>48500</v>
       </c>
       <c r="J59" s="3">
+        <v>48600</v>
+      </c>
+      <c r="K59" s="3">
         <v>35500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>230800</v>
+      </c>
+      <c r="E60" s="3">
         <v>131900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>146100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>106500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,53 +3787,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1180200</v>
+        <v>1367600</v>
       </c>
       <c r="E61" s="3">
-        <v>1253800</v>
+        <v>1368100</v>
       </c>
       <c r="F61" s="3">
-        <v>1163300</v>
+        <v>1443000</v>
       </c>
       <c r="G61" s="3">
-        <v>908000</v>
+        <v>1344000</v>
       </c>
       <c r="H61" s="3">
-        <v>878500</v>
+        <v>1066500</v>
       </c>
       <c r="I61" s="3">
-        <v>835700</v>
+        <v>1036300</v>
       </c>
       <c r="J61" s="3">
+        <v>965300</v>
+      </c>
+      <c r="K61" s="3">
         <v>634600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>527700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>522600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>521900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>524800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>503600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>364800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,53 +3852,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>256600</v>
+        <v>51900</v>
       </c>
       <c r="E62" s="3">
-        <v>286100</v>
+        <v>62700</v>
       </c>
       <c r="F62" s="3">
-        <v>295500</v>
+        <v>76100</v>
       </c>
       <c r="G62" s="3">
-        <v>253100</v>
+        <v>99400</v>
       </c>
       <c r="H62" s="3">
-        <v>256400</v>
+        <v>74200</v>
       </c>
       <c r="I62" s="3">
-        <v>235200</v>
+        <v>78400</v>
       </c>
       <c r="J62" s="3">
+        <v>87200</v>
+      </c>
+      <c r="K62" s="3">
         <v>211000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>190300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>121100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>149300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>214000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>35800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1641400</v>
+        <v>1656200</v>
       </c>
       <c r="E66" s="3">
-        <v>1760900</v>
+        <v>1568700</v>
       </c>
       <c r="F66" s="3">
-        <v>1643300</v>
+        <v>1686000</v>
       </c>
       <c r="G66" s="3">
-        <v>1318500</v>
+        <v>1565300</v>
       </c>
       <c r="H66" s="3">
-        <v>1287400</v>
+        <v>1257800</v>
       </c>
       <c r="I66" s="3">
-        <v>1224200</v>
+        <v>1232300</v>
       </c>
       <c r="J66" s="3">
+        <v>1167200</v>
+      </c>
+      <c r="K66" s="3">
         <v>952800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>788200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>706000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>738400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>808300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>620800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>469600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4206,14 +4374,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>283200</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>204900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-47800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-40300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-113800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-16800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-40900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-101400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-97300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-90600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>514800</v>
+      </c>
+      <c r="E76" s="3">
         <v>490500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>457500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>447100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>465900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>448000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>433200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>424100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>342100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>400000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>365900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>304900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-94100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-88500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>37500</v>
+        <v>17600</v>
       </c>
       <c r="E81" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F81" s="3">
         <v>7500</v>
       </c>
-      <c r="F81" s="3">
-        <v>-27000</v>
-      </c>
       <c r="G81" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="H81" s="3">
         <v>5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>67500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-97000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>84300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>59900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17200</v>
+        <v>13700</v>
       </c>
       <c r="E83" s="3">
-        <v>16100</v>
+        <v>13000</v>
       </c>
       <c r="F83" s="3">
-        <v>15600</v>
+        <v>11400</v>
       </c>
       <c r="G83" s="3">
+        <v>8800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K83" s="3">
+        <v>8800</v>
+      </c>
+      <c r="L83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="M83" s="3">
         <v>13700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>11400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>8800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>7100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6800</v>
       </c>
       <c r="N83" s="3">
         <v>6800</v>
       </c>
       <c r="O83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-95400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-141900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-158300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-53900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-319400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-124400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5597,19 +5831,22 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-22500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,61 +6037,64 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-81300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>122000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>262900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>31500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>42600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>190000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>295400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>198400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>125700</v>
-      </c>
-      <c r="R100" s="3">
-        <v>19700</v>
       </c>
       <c r="S100" s="3">
         <v>19700</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>19700</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -5856,31 +6102,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-111200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>134900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-115200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-98000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>291100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>AMPS</t>
   </si>
@@ -656,300 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E8" s="3">
         <v>58700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>44000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20900</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4600</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E10" s="3">
         <v>46800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +985,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1038,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,40 +1119,43 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-25200</v>
       </c>
-      <c r="G14" s="3">
-        <v>4700</v>
-      </c>
       <c r="H14" s="3">
+        <v>23500</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-15500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>300</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
@@ -1145,96 +1164,102 @@
         <v>300</v>
       </c>
       <c r="P14" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>17200</v>
+        <v>18500</v>
       </c>
       <c r="E15" s="3">
         <v>17200</v>
       </c>
       <c r="F15" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G15" s="3">
         <v>16100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>6800</v>
       </c>
       <c r="O15" s="3">
         <v>6800</v>
       </c>
       <c r="P15" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q15" s="3">
         <v>5300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5400</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1280,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E17" s="3">
         <v>41300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14400</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>800</v>
+      </c>
+      <c r="E18" s="3">
         <v>17400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,180 +1442,187 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>18000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>66500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-104900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>77300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>60200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6700</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E21" s="3">
         <v>34300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4400</v>
-      </c>
       <c r="H21" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I21" s="3">
         <v>24500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>74800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-87100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>96700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>23300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E22" s="3">
         <v>21800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
       </c>
       <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1599,144 +1638,153 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>65600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-94700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>82300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-21000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1848,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="E26" s="3">
         <v>8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>67100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-96600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>81700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>60100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E27" s="3">
         <v>17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>67500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-97000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>84300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>59900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>22300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,138 +2256,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-18000</v>
-      </c>
       <c r="H32" s="3">
+        <v>800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-66500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>104900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-77300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-60200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6700</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-61500</v>
+      </c>
+      <c r="E33" s="3">
         <v>17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-97000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>84300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>59900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>22300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2460,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-61500</v>
+      </c>
+      <c r="E35" s="3">
         <v>17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-97000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>84300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>59900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>22300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2655,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E41" s="3">
         <v>96900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>173300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>160800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>290900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>295100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>318200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>326000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,56 +2789,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E43" s="3">
         <v>34300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2857,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2791,8 +2886,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2830,56 +2925,59 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E45" s="3">
         <v>6200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9200</v>
       </c>
       <c r="O45" s="3">
         <v>9200</v>
       </c>
       <c r="P45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>12400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,56 +2993,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E46" s="3">
         <v>138800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>119900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>216700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>228800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>98100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>106300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>93400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>215100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>315500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>316400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>335800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>344400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>58200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,35 +3061,38 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>3000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2200</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3025,56 +3129,59 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2132400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2019100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1933200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1929100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1792900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1557200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1494400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1099600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>788100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>764900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>746000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>745700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>727700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>522200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,62 +3191,65 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E49" s="3">
         <v>49200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>48500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>47100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>47400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>47800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>47600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11400</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3149,14 +3259,17 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,56 +3401,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E52" s="3">
         <v>20800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3537,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2349000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2240100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2131900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2218500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2090300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1784400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1735400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1657400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1376900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1130300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1106100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1104300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1113200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>809900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>586100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,56 +3659,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E57" s="3">
         <v>8900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,62 +3719,65 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>186800</v>
+      </c>
+      <c r="E58" s="3">
         <v>148900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>78100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>79700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>46500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>37800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>30000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>21200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>21100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>33900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3654,62 +3787,65 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E59" s="3">
         <v>59000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,56 +3861,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>329500</v>
+      </c>
+      <c r="E60" s="3">
         <v>230800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>131900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>146100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>68200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,56 +3929,59 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1388300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1367600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1368100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1443000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1344000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1066500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1036300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>965300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>634600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>527700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>522600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>521900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>524800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>503600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>364800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,56 +3997,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E62" s="3">
         <v>51900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>62700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>76100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>99400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>74200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>78400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>87200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>211000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>190300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>121100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>149300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>214000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>35800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4269,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1805500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1656200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1568700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1686000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1565300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1257800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1232300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1167200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>952800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>788200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>706000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>738400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>808300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>620800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>469600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4377,14 +4544,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>283200</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>204900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4635,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E72" s="3">
         <v>7500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-47800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-55300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-28100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-33500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-40300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-45900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-113800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-40900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-101400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-97300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-90600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +4907,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>455200</v>
+      </c>
+      <c r="E76" s="3">
         <v>514800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>490500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>457500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>447100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>465900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>448000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>433200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>424100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>342100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>400000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>365900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>304900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-94100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-88500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5043,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-61500</v>
+      </c>
+      <c r="E81" s="3">
         <v>17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-97000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>84300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>59900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>22300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,73 +5212,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E83" s="3">
         <v>13700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6800</v>
       </c>
       <c r="O83" s="3">
         <v>6800</v>
       </c>
       <c r="P83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5400</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5618,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E89" s="3">
         <v>21400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,73 +5714,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-23700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5916,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-95400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-141900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-158300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-55200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-53900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-319400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-124400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26600</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,8 +6039,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5834,19 +6067,22 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-22500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,64 +6282,67 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E100" s="3">
         <v>93000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-81300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>122000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>262900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>42600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>190000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>295400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>198400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>125700</v>
-      </c>
-      <c r="S100" s="3">
-        <v>19700</v>
       </c>
       <c r="T100" s="3">
         <v>19700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>19700</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6105,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6131,8 +6379,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6170,69 +6418,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-111200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>134900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-115200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-98000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>291100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
